--- a/survey_templates/041_online_dating_survey--survey_templates.xlsx
+++ b/survey_templates/041_online_dating_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,23 +515,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>survey_background</t>
+          <t>current_dating_app_usage</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>dating_apps_usage</t>
+          <t>How often do you use dating apps?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>what_is_our_survey_about</t>
+          <t>why_survey</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Why did you take this survey?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>why_survey</t>
+          <t>best_dating_app_feature</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>What is the most important feature in a dating app?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,23 +584,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>dating_app_preferences</t>
+          <t>online_relationships</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Have you ever had an online relationship?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,64 +612,64 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>best_dating_app_feature</t>
+          <t>single</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Are you currently single?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>online_relationships</t>
+          <t>age</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>What is your age?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>dating_app_preferences</t>
+          <t>gender</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>What is your gender?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>single</t>
+          <t>education_level</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>What is your educational background?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,58 +704,58 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>how_old</t>
+          <t>income</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>What is your annual income?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>age_range</t>
+          <t>current_city</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>What is your current city?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>gender</t>
+          <t>preferred_city</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Which city do you prefer for dating?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>education_level</t>
+          <t>device_used</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Which device do you use for dating apps?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>income</t>
+          <t>access_method</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>How do you access dating apps?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,30 +819,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>income_range</t>
+          <t>online_dating</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Have you ever been in an online relationship?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>current_city</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -853,24 +853,24 @@
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>preferred_city</t>
+          <t>none_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>None 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>device_used</t>
+          <t>none_3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>None 3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,182 +906,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>access_method</t>
+          <t>none_4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>None 4</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>online_dating</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,177 +965,177 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>dating_app_preferences_choices</t>
+          <t>current_dating_app_usage_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>dating_app_preferences_choices</t>
+          <t>current_dating_app_usage_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>best_dating_app_feature_choices</t>
+          <t>current_dating_app_usage_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>best_dating_app_feature_choices</t>
+          <t>current_dating_app_usage_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>online_relationships_choices</t>
+          <t>current_dating_app_usage_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>online_relationships_choices</t>
+          <t>best_dating_app_feature_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>matching_algorithm</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Matching algorithm</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>dating_app_preferences_choices</t>
+          <t>best_dating_app_feature_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>user_interface</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>User interface</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>dating_app_preferences_choices</t>
+          <t>best_dating_app_feature_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>communication_tools</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Communication tools</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>single_choices</t>
+          <t>best_dating_app_feature_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>safety_and_security</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Safety and security</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>single_choices</t>
+          <t>best_dating_app_feature_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>age_range_choices</t>
+          <t>online_relationships_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1313,7 +1152,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>age_range_choices</t>
+          <t>online_relationships_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1330,7 +1169,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>gender_choices</t>
+          <t>single_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1347,7 +1186,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>gender_choices</t>
+          <t>single_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1364,245 +1203,245 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>education_level_choices</t>
+          <t>gender_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>education_level_choices</t>
+          <t>gender_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>income_range_choices</t>
+          <t>gender_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>non-binary</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Non-binary</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>income_range_choices</t>
+          <t>education_level_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>high_school</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>High school</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>device_used_choices</t>
+          <t>education_level_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>college/university</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>College/University</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>device_used_choices</t>
+          <t>education_level_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>postgraduate</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Postgraduate</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>access_method_choices</t>
+          <t>education_level_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>access_method_choices</t>
+          <t>device_used_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>mobile_phone</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Mobile phone</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>online_dating_choices</t>
+          <t>device_used_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>tablet</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Tablet</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>online_dating_choices</t>
+          <t>device_used_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>computer</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Computer</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>none_choices</t>
+          <t>device_used_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>none_choices</t>
+          <t>access_method_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>mobile_data</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Mobile data</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>none_choices</t>
+          <t>access_method_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>wi-fi</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Wi-Fi</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>none_choices</t>
+          <t>access_method_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>none_choices</t>
+          <t>online_dating_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1619,7 +1458,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>none_choices</t>
+          <t>online_dating_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1670,7 +1509,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>none_choices</t>
+          <t>none_2_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1687,7 +1526,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>none_choices</t>
+          <t>none_2_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1704,7 +1543,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>none_choices</t>
+          <t>none_3_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1721,7 +1560,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>none_choices</t>
+          <t>none_3_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1730,6 +1569,40 @@
         </is>
       </c>
       <c r="C37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>none_4_choices</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>none_4_choices</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
         <is>
           <t>No</t>
         </is>
